--- a/DATA/production_capacity_scenarios/ARCHIVE/pivoted_results.xlsx
+++ b/DATA/production_capacity_scenarios/ARCHIVE/pivoted_results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/production_capacity_scenarios/ARCHIVE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_5039F86C1E68F00E62355476585DCE3A8746C32A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE05BA9D-5365-4835-96B9-B021315A1E3D}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="11_5039F86C1E68F00E62355476585DCE3A8746C32A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FC427AA-3D41-43E3-86F8-0818C9E83CC1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -253,10 +253,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -544,7 +540,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -576,7 +571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>60</v>
       </c>
@@ -599,7 +594,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>111</v>
       </c>
@@ -622,7 +617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>32</v>
       </c>
@@ -645,7 +640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>91</v>
       </c>
@@ -668,7 +663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>177</v>
       </c>
@@ -691,7 +686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -714,7 +709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -737,7 +732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>47</v>
       </c>
@@ -760,7 +755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46</v>
       </c>
@@ -783,7 +778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>48</v>
       </c>
@@ -829,7 +824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -875,7 +870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>55</v>
       </c>
@@ -898,7 +893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>142</v>
       </c>
@@ -921,7 +916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>161</v>
       </c>
@@ -944,7 +939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>62</v>
       </c>
@@ -967,7 +962,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>113</v>
       </c>
@@ -990,7 +985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>92</v>
       </c>
@@ -1013,7 +1008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -1036,7 +1031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>33</v>
       </c>
@@ -1059,7 +1054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>143</v>
       </c>
@@ -1105,7 +1100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>61</v>
       </c>
@@ -1151,7 +1146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>162</v>
       </c>
@@ -1174,7 +1169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>178</v>
       </c>
@@ -1197,7 +1192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>63</v>
       </c>
@@ -1220,7 +1215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>64</v>
       </c>
@@ -1243,7 +1238,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>114</v>
       </c>
@@ -1266,7 +1261,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>94</v>
       </c>
@@ -1289,7 +1284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -1312,7 +1307,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>29</v>
       </c>
@@ -1335,7 +1330,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>39</v>
       </c>
@@ -1358,7 +1353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>144</v>
       </c>
@@ -1381,7 +1376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>179</v>
       </c>
@@ -1404,7 +1399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>6</v>
       </c>
@@ -1427,7 +1422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>30</v>
       </c>
@@ -1450,7 +1445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>40</v>
       </c>
@@ -1473,7 +1468,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>67</v>
       </c>
@@ -1496,7 +1491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>116</v>
       </c>
@@ -1519,7 +1514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>165</v>
       </c>
@@ -1542,7 +1537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>164</v>
       </c>
@@ -1588,7 +1583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>66</v>
       </c>
@@ -1611,7 +1606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>96</v>
       </c>
@@ -1657,7 +1652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>97</v>
       </c>
@@ -1703,7 +1698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>117</v>
       </c>
@@ -1726,7 +1721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>145</v>
       </c>
@@ -1749,7 +1744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>98</v>
       </c>
@@ -1772,7 +1767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>163</v>
       </c>
@@ -1795,7 +1790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>146</v>
       </c>
@@ -1818,7 +1813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>180</v>
       </c>
@@ -1841,7 +1836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>181</v>
       </c>
@@ -1864,7 +1859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>99</v>
       </c>
@@ -1887,7 +1882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>119</v>
       </c>
@@ -1910,7 +1905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>121</v>
       </c>
@@ -1933,7 +1928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>184</v>
       </c>
@@ -1956,7 +1951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>168</v>
       </c>
@@ -1979,7 +1974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>7</v>
       </c>
@@ -2002,7 +1997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>69</v>
       </c>
@@ -2025,7 +2020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>182</v>
       </c>
@@ -2048,7 +2043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>31</v>
       </c>
@@ -2071,7 +2066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>41</v>
       </c>
@@ -2094,7 +2089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>42</v>
       </c>
@@ -2117,7 +2112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -2140,7 +2135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>70</v>
       </c>
@@ -2163,7 +2158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>118</v>
       </c>
@@ -2186,7 +2181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>100</v>
       </c>
@@ -2232,7 +2227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>147</v>
       </c>
@@ -2255,7 +2250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>166</v>
       </c>
@@ -2278,7 +2273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>167</v>
       </c>
@@ -2324,7 +2319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>73</v>
       </c>
@@ -2347,7 +2342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>124</v>
       </c>
@@ -2370,7 +2365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>126</v>
       </c>
@@ -2393,7 +2388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>12</v>
       </c>
@@ -2416,7 +2411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>10</v>
       </c>
@@ -2439,7 +2434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>101</v>
       </c>
@@ -2462,7 +2457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>186</v>
       </c>
@@ -2485,7 +2480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>34</v>
       </c>
@@ -2508,7 +2503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>49</v>
       </c>
@@ -2531,7 +2526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>50</v>
       </c>
@@ -2554,7 +2549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>187</v>
       </c>
@@ -2577,7 +2572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>8</v>
       </c>
@@ -2600,7 +2595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>57</v>
       </c>
@@ -2669,7 +2664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>36</v>
       </c>
@@ -2692,7 +2687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>122</v>
       </c>
@@ -2715,7 +2710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>148</v>
       </c>
@@ -2738,7 +2733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>169</v>
       </c>
@@ -2761,7 +2756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>71</v>
       </c>
@@ -2807,7 +2802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>74</v>
       </c>
@@ -2830,7 +2825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>185</v>
       </c>
@@ -2853,7 +2848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>9</v>
       </c>
@@ -2876,7 +2871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>123</v>
       </c>
@@ -2899,7 +2894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -2945,7 +2940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>75</v>
       </c>
@@ -2991,7 +2986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>150</v>
       </c>
@@ -3014,7 +3009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>170</v>
       </c>
@@ -3037,7 +3032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>171</v>
       </c>
@@ -3060,7 +3055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>127</v>
       </c>
@@ -3083,7 +3078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>103</v>
       </c>
@@ -3106,7 +3101,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>173</v>
       </c>
@@ -3129,7 +3124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>77</v>
       </c>
@@ -3152,7 +3147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>15</v>
       </c>
@@ -3175,7 +3170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>128</v>
       </c>
@@ -3198,7 +3193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>172</v>
       </c>
@@ -3221,7 +3216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>188</v>
       </c>
@@ -3244,7 +3239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>76</v>
       </c>
@@ -3267,7 +3262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>78</v>
       </c>
@@ -3290,7 +3285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>129</v>
       </c>
@@ -3313,7 +3308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>174</v>
       </c>
@@ -3359,7 +3354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>16</v>
       </c>
@@ -3382,7 +3377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>13</v>
       </c>
@@ -3405,7 +3400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>37</v>
       </c>
@@ -3428,7 +3423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>44</v>
       </c>
@@ -3451,7 +3446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>45</v>
       </c>
@@ -3497,7 +3492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>104</v>
       </c>
@@ -3520,7 +3515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>151</v>
       </c>
@@ -3543,7 +3538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>152</v>
       </c>
@@ -3566,7 +3561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>189</v>
       </c>
@@ -3589,7 +3584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>130</v>
       </c>
@@ -3612,7 +3607,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>105</v>
       </c>
@@ -3635,7 +3630,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>131</v>
       </c>
@@ -3658,7 +3653,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>175</v>
       </c>
@@ -3681,7 +3676,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>191</v>
       </c>
@@ -3704,7 +3699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>19</v>
       </c>
@@ -3727,7 +3722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>190</v>
       </c>
@@ -3750,7 +3745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>176</v>
       </c>
@@ -3773,7 +3768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>38</v>
       </c>
@@ -3796,7 +3791,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>155</v>
       </c>
@@ -3819,7 +3814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>53</v>
       </c>
@@ -3842,7 +3837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>106</v>
       </c>
@@ -3865,7 +3860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>153</v>
       </c>
@@ -3888,7 +3883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>58</v>
       </c>
@@ -3934,7 +3929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>20</v>
       </c>
@@ -3957,7 +3952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>17</v>
       </c>
@@ -3980,7 +3975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>43</v>
       </c>
@@ -4026,7 +4021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>79</v>
       </c>
@@ -4049,7 +4044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>59</v>
       </c>
@@ -4072,7 +4067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>80</v>
       </c>
@@ -4118,7 +4113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>82</v>
       </c>
@@ -4141,7 +4136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>83</v>
       </c>
@@ -4164,7 +4159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>84</v>
       </c>
@@ -4210,7 +4205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>192</v>
       </c>
@@ -4233,7 +4228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>132</v>
       </c>
@@ -4256,7 +4251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>193</v>
       </c>
@@ -4279,7 +4274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>25</v>
       </c>
@@ -4302,7 +4297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>133</v>
       </c>
@@ -4325,7 +4320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>156</v>
       </c>
@@ -4348,7 +4343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>194</v>
       </c>
@@ -4371,7 +4366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>27</v>
       </c>
@@ -4394,7 +4389,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>23</v>
       </c>
@@ -4417,7 +4412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>86</v>
       </c>
@@ -4440,7 +4435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>89</v>
       </c>
@@ -4463,7 +4458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>90</v>
       </c>
@@ -4486,7 +4481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>141</v>
       </c>
@@ -4509,7 +4504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>157</v>
       </c>
@@ -4532,7 +4527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>159</v>
       </c>
@@ -4555,7 +4550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>0</v>
       </c>
@@ -4578,7 +4573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>21</v>
       </c>
@@ -4601,7 +4596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>22</v>
       </c>
@@ -4647,7 +4642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>28</v>
       </c>
@@ -4693,7 +4688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>107</v>
       </c>
@@ -4716,7 +4711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>108</v>
       </c>
@@ -4739,7 +4734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>88</v>
       </c>
@@ -4762,7 +4757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>109</v>
       </c>
@@ -4785,7 +4780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>110</v>
       </c>
@@ -4808,7 +4803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>87</v>
       </c>
@@ -4831,7 +4826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>134</v>
       </c>
@@ -4854,7 +4849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>135</v>
       </c>
@@ -4877,7 +4872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>24</v>
       </c>
@@ -4900,7 +4895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>137</v>
       </c>
@@ -4923,7 +4918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>138</v>
       </c>
@@ -4946,7 +4941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>139</v>
       </c>
@@ -4969,7 +4964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>140</v>
       </c>
@@ -4992,7 +4987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>136</v>
       </c>
@@ -5015,7 +5010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>160</v>
       </c>
@@ -5038,7 +5033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>158</v>
       </c>
@@ -5063,11 +5058,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G196" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Other/Not identified/Not known"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G196">
       <sortCondition ref="C1:C196"/>
     </sortState>
